--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\docs\Projects\DMP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\docs\Projects\PythonProject\DMP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C66949D-806E-4A92-BCE8-5AA840860B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="15">
   <si>
     <t>Dataset</t>
   </si>
@@ -70,8 +69,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,16 +83,30 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -133,117 +146,77 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -261,10 +234,96 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -277,9 +336,11 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -290,111 +351,53 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -402,6 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -409,23 +413,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -728,129 +764,201 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>0.81499999999999995</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>0.56399999999999995</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>0.66700000000000004</v>
       </c>
-      <c r="F2" s="16">
-        <v>0.53500000000000003</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0.29099999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="2">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="J2">
+        <f>ROUND(C2,2)</f>
+        <v>0.82</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2:O2" si="0">ROUND(D2,2)</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="0"/>
+        <v>0.67</v>
+      </c>
+      <c r="M2">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+      <c r="N2">
+        <f t="shared" si="0"/>
+        <v>0.37</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>0.79300000000000004</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="6">
         <v>0.59</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="16">
         <v>0.67600000000000005</v>
       </c>
-      <c r="F3" s="17">
-        <v>0.65800000000000003</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.217</v>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.33</v>
       </c>
       <c r="H3" s="7">
-        <v>0.32700000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+        <v>0.497</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J13" si="1">ROUND(C3,2)</f>
+        <v>0.79</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K13" si="2">ROUND(D3,2)</f>
+        <v>0.59</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L13" si="3">ROUND(E3,2)</f>
+        <v>0.68</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M13" si="4">ROUND(F3,2)</f>
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N13" si="5">ROUND(G3,2)</f>
+        <v>0.33</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O13" si="6">ROUND(H3,2)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>0.71</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="6">
         <v>0.56399999999999995</v>
       </c>
       <c r="E4" s="7">
         <v>0.629</v>
       </c>
-      <c r="F4" s="17">
-        <v>0.54200000000000004</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.22600000000000001</v>
+      <c r="F4" s="5">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.4</v>
       </c>
       <c r="H4" s="7">
-        <v>0.31900000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>0.71</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="2"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="3"/>
+        <v>0.63</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="4"/>
+        <v>0.96</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="6"/>
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="8">
@@ -862,99 +970,195 @@
       <c r="E5" s="10">
         <v>0.63600000000000001</v>
       </c>
-      <c r="F5" s="18">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0.27200000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="F5" s="20">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="G5" s="21">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="H5" s="22">
+        <v>0.627</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>0.78</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="2"/>
+        <v>0.54</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="3"/>
+        <v>0.64</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="4"/>
+        <v>0.98</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="6"/>
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>0.78900000000000003</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>0.46899999999999997</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>0.58799999999999997</v>
       </c>
-      <c r="F6" s="16">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="F6" s="2">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>0.79</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>0.47</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>0.59</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="4"/>
+        <v>0.74</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="5"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="6"/>
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>0.76</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="6">
         <v>0.59399999999999997</v>
       </c>
       <c r="E7" s="7">
         <v>0.66700000000000004</v>
       </c>
-      <c r="F7" s="17">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.4</v>
+      <c r="F7" s="5">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.7</v>
       </c>
       <c r="H7" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>0.76</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>0.59</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>0.67</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="4"/>
+        <v>0.85</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="6"/>
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>0.75</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="6">
         <v>0.65600000000000003</v>
       </c>
       <c r="E8" s="7">
         <v>0.7</v>
       </c>
-      <c r="F8" s="17">
-        <v>0.26800000000000002</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.22</v>
+      <c r="F8" s="5">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.56000000000000005</v>
       </c>
       <c r="H8" s="7">
-        <v>0.24199999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>0.66</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="4"/>
+        <v>0.68</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="5"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="6"/>
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="8">
@@ -963,102 +1167,198 @@
       <c r="D9" s="9">
         <v>0.78100000000000003</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="17">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F9" s="18">
-        <v>0.26700000000000002</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0.24</v>
-      </c>
-      <c r="H9" s="10">
-        <v>0.253</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="F9" s="20">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H9" s="22">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>0.89</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>0.78</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>0.83</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="6"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>0.90500000000000003</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>0.51400000000000001</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>0.65500000000000003</v>
       </c>
-      <c r="F10" s="16">
-        <v>0.32400000000000001</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0.247</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="F10" s="18">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>0.91</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>0.51</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>0.66</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>0.94</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="5"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="6"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>0.88200000000000001</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="6">
         <v>0.81100000000000005</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="16">
         <v>0.84499999999999997</v>
       </c>
-      <c r="F11" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.36399999999999999</v>
+      <c r="F11" s="19">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.6</v>
       </c>
       <c r="H11" s="7">
-        <v>0.42099999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>0.81</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="4"/>
+        <v>0.83</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="6"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>0.88200000000000001</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="6">
         <v>0.81100000000000005</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="16">
         <v>0.84499999999999997</v>
       </c>
-      <c r="F12" s="17">
-        <v>0.57099999999999995</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.436</v>
-      </c>
-      <c r="H12" s="7">
-        <v>0.495</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="19">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>0.81</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="4"/>
+        <v>0.88</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="5"/>
+        <v>0.67</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="6"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="8">
@@ -1070,17 +1370,549 @@
       <c r="E13" s="10">
         <v>0.77100000000000002</v>
       </c>
-      <c r="F13" s="18">
-        <v>0.47399999999999998</v>
+      <c r="F13" s="15">
+        <v>0.89500000000000002</v>
       </c>
       <c r="G13" s="9">
-        <v>0.32700000000000001</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H13" s="10">
-        <v>0.38700000000000001</v>
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>0.73</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>0.77</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="4"/>
+        <v>0.9</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="5"/>
+        <v>0.62</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="6"/>
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0.64</v>
+      </c>
+      <c r="F19" s="20">
+        <v>0.98</v>
+      </c>
+      <c r="G19" s="21">
+        <v>0.46</v>
+      </c>
+      <c r="H19" s="22">
+        <v>0.63</v>
+      </c>
+      <c r="J19" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="K19" s="24">
+        <v>0.68</v>
+      </c>
+      <c r="L19" s="25">
+        <v>0.78</v>
+      </c>
+      <c r="M19" s="23">
+        <v>0.87</v>
+      </c>
+      <c r="N19" s="24">
+        <v>0.41</v>
+      </c>
+      <c r="O19" s="25">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.79</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.59</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.41</v>
+      </c>
+      <c r="J20" s="26"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="28"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="J21" s="29"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="31"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.66</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.68</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="J22" s="29"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="31"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.89</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0.83</v>
+      </c>
+      <c r="F23" s="20">
+        <v>1</v>
+      </c>
+      <c r="G23" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H23" s="22">
+        <v>0.95</v>
+      </c>
+      <c r="J23" s="23">
+        <v>0.96</v>
+      </c>
+      <c r="K23" s="24">
+        <v>0.84</v>
+      </c>
+      <c r="L23" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="M23" s="23">
+        <v>1</v>
+      </c>
+      <c r="N23" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="O23" s="25">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="F24" s="18">
+        <v>0.94</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="28"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.81</v>
+      </c>
+      <c r="E25" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="F25" s="19">
+        <v>0.83</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="J25" s="29"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.81</v>
+      </c>
+      <c r="E26" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0.88</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="H26" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="J26" s="29"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.73</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.77</v>
+      </c>
+      <c r="F27" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0.62</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.73</v>
+      </c>
+      <c r="J27" s="23">
+        <v>0.91</v>
+      </c>
+      <c r="K27" s="33">
+        <v>0.81</v>
+      </c>
+      <c r="L27" s="25">
+        <v>0.86</v>
+      </c>
+      <c r="M27" s="23">
+        <v>0.87</v>
+      </c>
+      <c r="N27" s="24">
+        <v>0.62</v>
+      </c>
+      <c r="O27" s="25">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="J29">
+        <f>C19-J19</f>
+        <v>-0.12</v>
+      </c>
+      <c r="K29">
+        <f t="shared" ref="K29:O29" si="7">D19-K19</f>
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="7"/>
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="7"/>
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="7"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="7"/>
+        <v>6.9999999999999951E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="10:15" x14ac:dyDescent="0.35">
+      <c r="J33">
+        <f t="shared" ref="J30:J35" si="8">C23-J23</f>
+        <v>-6.9999999999999951E-2</v>
+      </c>
+      <c r="K33">
+        <f t="shared" ref="K30:K36" si="9">D23-K23</f>
+        <v>-5.9999999999999942E-2</v>
+      </c>
+      <c r="L33">
+        <f t="shared" ref="L30:L36" si="10">E23-L23</f>
+        <v>-7.0000000000000062E-2</v>
+      </c>
+      <c r="M33">
+        <f t="shared" ref="M30:M36" si="11">F23-M23</f>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f t="shared" ref="N30:N36" si="12">G23-N23</f>
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="O33">
+        <f t="shared" ref="O30:O36" si="13">H23-O23</f>
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="37" spans="10:15" x14ac:dyDescent="0.35">
+      <c r="J37">
+        <f t="shared" ref="J37" si="14">C27-J27</f>
+        <v>-9.000000000000008E-2</v>
+      </c>
+      <c r="K37">
+        <f t="shared" ref="K37" si="15">D27-K27</f>
+        <v>-8.0000000000000071E-2</v>
+      </c>
+      <c r="L37">
+        <f t="shared" ref="L37" si="16">E27-L27</f>
+        <v>-8.9999999999999969E-2</v>
+      </c>
+      <c r="M37">
+        <f t="shared" ref="M37" si="17">F27-M27</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="N37">
+        <f t="shared" ref="N37" si="18">G27-N27</f>
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <f t="shared" ref="O37" si="19">H27-O27</f>
+        <v>1.0000000000000009E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>